--- a/LubanTables/Datas/__tables__.xlsx
+++ b/LubanTables/Datas/__tables__.xlsx
@@ -14,8 +14,15 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors/>
+  <commentList/>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -117,6 +124,15 @@
   </si>
   <si>
     <t>ItemConfig</t>
+  </si>
+  <si>
+    <t>grid_plane.xlsx</t>
+  </si>
+  <si>
+    <t>GridPlaneConfig</t>
+  </si>
+  <si>
+    <t>data.TbGridPlane</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="14.250000"/>
   <cols>
     <col min="2" max="2" width="20.37999916" customWidth="1" outlineLevel="0"/>
@@ -1142,9 +1158,24 @@
         <v>29</v>
       </c>
     </row>
+    <row r="5" spans="1:11">
+      <c r="B5" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>